--- a/input/Glossaire CareSets V1.xlsx
+++ b/input/Glossaire CareSets V1.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -186,6 +186,20 @@
       <color rgb="FFFF8C00"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -300,7 +314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -428,6 +442,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5863,7 +5890,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C2" s="48" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>Administration Date</t>
         </is>
@@ -5874,7 +5901,7 @@
       <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="46" t="inlineStr">
+      <c r="G2" s="52" t="inlineStr">
         <is>
           <t>date à laquelle un produit ou un vaccin est administré au patient par le Performer</t>
         </is>
@@ -5884,7 +5911,7 @@
           <t>Une période de la vie peut aussi être mentionnée si les dates sont inconnues (pendant  l’enfance, à l’adolescence…)</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>datum waarop een product of vaccin door de Performer aan de patiënt is toegediend</t>
         </is>
@@ -5894,12 +5921,12 @@
           <t>Indien de data onbekend zijn, kan ook een levensfase worden vermeld (tijdens de kindertijd, in de adolescentie…)</t>
         </is>
       </c>
-      <c r="K2" s="48" t="inlineStr">
+      <c r="K2" s="51" t="inlineStr">
         <is>
           <t>date on which a product or vaccine is administered to the patient by the Performer</t>
         </is>
       </c>
-      <c r="L2" s="48" t="inlineStr">
+      <c r="L2" s="51" t="inlineStr">
         <is>
           <t>For vaccines, a life period may also be recorded when the exact date is unknown (during childhood, adolescence, …).</t>
         </is>
@@ -5922,7 +5949,7 @@
       <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="46" t="inlineStr">
+      <c r="G3" s="52" t="inlineStr">
         <is>
           <t>personne qui rapporte l'information enregistrée dans le CareSet</t>
         </is>
@@ -5933,7 +5960,7 @@
 Toutefois, lorsqu’il s’agit d’un parent ou proche, seul le rôle sera encodé (ex : père, mère, voisin, aidant-proche, ami, …) pour répondre aux exigences RGPD. Dans un premier temps, on utilisera le texte inspiré du futur ValueSet et par la suite, on utilisera le ValueSet « VS_PatientRelationshipType » en cours de validation chez SNOMED/ FHIR international.  Ce sera un ValueSet transversal (ex : utilisé aussi pour les antécédents familiaux). Attention, actuellement,  il n’y a pas de référence vers un CareSet administratif.</t>
         </is>
       </c>
-      <c r="I3" s="47" t="inlineStr">
+      <c r="I3" s="53" t="inlineStr">
         <is>
           <t>persoon die de in de CareSet geregistreerde informatie rapporteert</t>
         </is>
@@ -5944,12 +5971,12 @@
 Wanneer het echter om een familielid of naaste gaat, wordt alleen de rol ingevoerd (bijv.: vader, moeder, buur, mantelzorger, vriend, …) om te voldoen aan de AVG-vereisten. In eerste instantie zal de tekst worden gebruikt die is geïnspireerd op de toekomstige ValueSet en daarna zal de ValueSet ‘VS_PatientRelationshipType’ worden gebruikt, die momenteel wordt gevalideerd bij SNOMED/FHIR International. Dit wordt een transversale ValueSet (bijv. ook gebruikt voor de familiegeschiedenis). Let op: momenteel is er geen verwijzing naar een administratieve CareSet."</t>
         </is>
       </c>
-      <c r="K3" s="48" t="inlineStr">
+      <c r="K3" s="51" t="inlineStr">
         <is>
           <t>person who reports the information recorded in the CareSet</t>
         </is>
       </c>
-      <c r="L3" s="48" t="inlineStr">
+      <c r="L3" s="51" t="inlineStr">
         <is>
           <t>For example: the patient, the general practitioner, a relative, or the professional recording the information themselves.</t>
         </is>
@@ -5961,45 +5988,50 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>Recorder</t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Recorder</t>
-        </is>
-      </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="46" t="inlineStr">
+      <c r="G4" s="52" t="inlineStr">
         <is>
           <t>professionnel de la santé qui enregistre le contenu du CareSet et en assume la responsabilité</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Toutefois, lorsqu’il s’agit d’un parent ou proche, seul le rôle sera encodé (ex : père, mère, voisin, aidant-proche, ami, …) pour répondre aux exigences RGPD. Dans un premier temps, on utilisera le texte inspiré du futur ValueSet et par la suite, on utilisera le ValueSet « VS_PatientRelationshipType » en cours de validation chez SNOMED/ FHIR international.  Ce sera un ValueSet transversal (ex : utilisé aussi pour les antécédents familiaux). Attention, actuellement,  il n’y a pas de référence vers un CareSet administratif.</t>
-        </is>
-      </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="H4" s="47" t="inlineStr">
+        <is>
+          <t>L'identifiant unique doit être le N° de registre national (NISS) ou le numéro BIS du professionnel.</t>
+        </is>
+      </c>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>zorgverlener die de inhoud van de CareSet vastlegt en er de verantwoordelijkheid voor draagt</t>
         </is>
       </c>
-      <c r="J4" s="40" t="inlineStr">
-        <is>
-          <t>Wanneer het echter om een ouder of naaste gaat, wordt alleen de rol ingevoerd (bijv.: vader, moeder, buur, mantelzorger, vriend, …) om te voldoen aan de AVG-vereisten. In eerste instantie zal de tekst worden gebruikt die is geïnspireerd op de toekomstige ValueSet en daarna zal de ValueSet „VS_PatientRelationshipType“ worden gebruikt, die momenteel wordt gevalideerd bij SNOMED/FHIR International. Dit wordt een transversale ValueSet (bijv. ook gebruikt voor de familiegeschiedenis). Let op: momenteel is er geen verwijzing naar een administratieve CareSet.</t>
-        </is>
-      </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>De unieke identificatiecode moet het nationale registratienummer (NISS) of het BIS-nummer van de beroepsbeoefenaar zijn.</t>
+        </is>
+      </c>
+      <c r="K4" s="51" t="inlineStr">
         <is>
           <t>healthcare professional who records the content of the CareSet and takes responsibility for it</t>
+        </is>
+      </c>
+      <c r="L4" s="48" t="inlineStr">
+        <is>
+          <t>The unique identifier is the professional's national register number (NISS) or BIS number.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -6014,7 +6046,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C5" s="48" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Body Laterality</t>
         </is>
@@ -6025,7 +6057,7 @@
       <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="46" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>côté du corps auquel se rapporte l'information enregistrée</t>
         </is>
@@ -6035,7 +6067,7 @@
           <t>(à droite, à gauche, les deux)</t>
         </is>
       </c>
-      <c r="I5" s="47" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>zijde van het lichaam waarop de geregistreerde informatie betrekking heeft</t>
         </is>
@@ -6045,12 +6077,12 @@
           <t>Links,rechts,beiden</t>
         </is>
       </c>
-      <c r="K5" s="48" t="inlineStr">
+      <c r="K5" s="51" t="inlineStr">
         <is>
           <t>side of the body to which the recorded information refers</t>
         </is>
       </c>
-      <c r="L5" s="48" t="inlineStr">
+      <c r="L5" s="51" t="inlineStr">
         <is>
           <t>Right, left, or both.</t>
         </is>
@@ -6062,7 +6094,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>Body Location</t>
         </is>
@@ -6078,7 +6110,7 @@
       <c r="F6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="46" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>partie du corps à laquelle se rapporte l'information enregistrée</t>
         </is>
@@ -6088,7 +6120,7 @@
           <t xml:space="preserve"> (tête, jambe, fémur, cœur, …)</t>
         </is>
       </c>
-      <c r="I6" s="48" t="inlineStr">
+      <c r="I6" s="51" t="inlineStr">
         <is>
           <t>lichaamsdeel waarop de geregistreerde informatie betrekking heeft</t>
         </is>
@@ -6098,12 +6130,12 @@
           <t xml:space="preserve"> (hoofd, been, dijbeen, hart, …)</t>
         </is>
       </c>
-      <c r="K6" s="48" t="inlineStr">
+      <c r="K6" s="51" t="inlineStr">
         <is>
           <t>part of the body to which the recorded information refers</t>
         </is>
       </c>
-      <c r="L6" s="48" t="inlineStr">
+      <c r="L6" s="51" t="inlineStr">
         <is>
           <t>For example: head, leg, femur, heart, …</t>
         </is>
@@ -6115,7 +6147,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C7" s="48" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Body Topography</t>
         </is>
@@ -6126,7 +6158,7 @@
       <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="46" t="inlineStr">
+      <c r="G7" s="52" t="inlineStr">
         <is>
           <t>position relative, à l'intérieur de la partie du corps concernée, du siège de l'information enregistrée</t>
         </is>
@@ -6136,7 +6168,7 @@
           <t>telle que supérieure/inférieure, médiale/latérale ou interne/externe.</t>
         </is>
       </c>
-      <c r="I7" s="47" t="inlineStr">
+      <c r="I7" s="53" t="inlineStr">
         <is>
           <t>relatieve positie, binnen het betrokken lichaamsdeel, van de plaats waarop de geregistreerde informatie betrekking heeft</t>
         </is>
@@ -6146,12 +6178,12 @@
           <t>zoals bovenste/onderste, mediaal/lateraal of inwendig/uitwendig.</t>
         </is>
       </c>
-      <c r="K7" s="48" t="inlineStr">
+      <c r="K7" s="51" t="inlineStr">
         <is>
           <t>relative position, within the body part concerned, of the site to which the recorded information refers</t>
         </is>
       </c>
-      <c r="L7" s="48" t="inlineStr">
+      <c r="L7" s="51" t="inlineStr">
         <is>
           <t>For example: superior/inferior, medial/lateral, internal/external.</t>
         </is>
@@ -6181,7 +6213,7 @@
           <t>*</t>
         </is>
       </c>
-      <c r="G8" s="49" t="inlineStr">
+      <c r="G8" s="54" t="inlineStr">
         <is>
           <t>identifiant qui désigne une instance de CareSet et qui est unique dans l'espace de nommage du système qui l'attribue</t>
         </is>
@@ -6191,7 +6223,7 @@
           <t>Normalement un seul identifiant est admis mais dans certains cas,  plusieurs identifiants seront permit (par ex : numéro de passeport, numéro niss dans le cs Bepatient, id Belrai)</t>
         </is>
       </c>
-      <c r="I8" s="48" t="inlineStr">
+      <c r="I8" s="51" t="inlineStr">
         <is>
           <t>identificatie die een CareSet-instantie aanduidt en uniek is binnen de naamruimte van het systeem dat haar toekent</t>
         </is>
@@ -6201,7 +6233,7 @@
           <t>Normaal gesproken is slechts één identificatiecode toegestaan, maar in bepaalde gevallen zijn meerdere identificatiecodes toegestaan (bijv.: paspoortnummer, NISS-nummer in het Bepatient-systeem, Belrai-ID)</t>
         </is>
       </c>
-      <c r="K8" s="48" t="inlineStr">
+      <c r="K8" s="51" t="inlineStr">
         <is>
           <t>identifier that designates a CareSet instance and is unique within the namespace of the system that assigns it</t>
         </is>
@@ -6226,7 +6258,7 @@
           <t>*</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G9" s="55" t="inlineStr">
         <is>
           <t>attribut classant un élément de données selon sa signification clinique ou fonctionnelle, permettant d'en regrouper les occurrences</t>
         </is>
@@ -6236,13 +6268,13 @@
           <t>Permet de distinguer les différents groupes. Est un instrument de recherche. "MetaData"</t>
         </is>
       </c>
-      <c r="I9" s="47" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>attribuut dat een gegevenselement indeelt naar zijn klinische of functionele betekenis, waardoor de voorkomens ervan gegroepeerd kunnen worden</t>
         </is>
       </c>
       <c r="J9" s="1" t="n"/>
-      <c r="K9" s="48" t="inlineStr">
+      <c r="K9" s="51" t="inlineStr">
         <is>
           <t>attribute classifying a data element by its clinical or functional meaning, allowing its occurrences to be grouped</t>
         </is>
@@ -6254,7 +6286,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C10" s="48" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>Clinical Status</t>
         </is>
@@ -6265,7 +6297,7 @@
       <c r="F10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="46" t="inlineStr">
+      <c r="G10" s="52" t="inlineStr">
         <is>
           <t>état rendant compte de l'actualité clinique de l'information enregistrée</t>
         </is>
@@ -6275,17 +6307,17 @@
           <t>Ex : active, inactive, completed, Entered_in_error (doit se trouver dans la description)</t>
         </is>
       </c>
-      <c r="I10" s="47" t="inlineStr">
+      <c r="I10" s="53" t="inlineStr">
         <is>
           <t>toestand die de klinische actualiteit van de geregistreerde informatie weergeeft</t>
         </is>
       </c>
-      <c r="K10" s="48" t="inlineStr">
+      <c r="K10" s="51" t="inlineStr">
         <is>
           <t>state expressing the clinical currency of the recorded information</t>
         </is>
       </c>
-      <c r="L10" s="48" t="inlineStr">
+      <c r="L10" s="51" t="inlineStr">
         <is>
           <t>For example: active, inactive, resolved, entered-in-error.</t>
         </is>
@@ -6308,17 +6340,17 @@
       <c r="F11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G11" s="52" t="inlineStr">
         <is>
           <t>valeur codée désignant le concept clinique auquel se rapporte l'information enregistrée</t>
         </is>
       </c>
-      <c r="I11" s="47" t="inlineStr">
+      <c r="I11" s="53" t="inlineStr">
         <is>
           <t>gecodeerde waarde die het klinische concept aanduidt waarop de geregistreerde informatie betrekking heeft</t>
         </is>
       </c>
-      <c r="K11" s="48" t="inlineStr">
+      <c r="K11" s="51" t="inlineStr">
         <is>
           <t>coded value designating the clinical concept to which the recorded information refers</t>
         </is>
@@ -6330,22 +6362,22 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C12" s="48" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>Device</t>
         </is>
       </c>
-      <c r="G12" s="48" t="inlineStr">
+      <c r="G12" s="51" t="inlineStr">
         <is>
           <t>instrument, appareil, équipement, logiciel ou autre article destiné par son fabricant à être utilisé à des fins médicales chez l'être humain</t>
         </is>
       </c>
-      <c r="I12" s="48" t="inlineStr">
+      <c r="I12" s="51" t="inlineStr">
         <is>
           <t>instrument, toestel, apparaat, software of ander artikel dat door de fabrikant bestemd is om bij de mens voor medische doeleinden te worden gebruikt</t>
         </is>
       </c>
-      <c r="K12" s="48" t="inlineStr">
+      <c r="K12" s="51" t="inlineStr">
         <is>
           <t>instrument, apparatus, appliance, software or other article intended by its manufacturer to be used for medical purposes in human beings</t>
         </is>
@@ -6370,7 +6402,7 @@
           <t>*</t>
         </is>
       </c>
-      <c r="G13" s="46" t="inlineStr">
+      <c r="G13" s="52" t="inlineStr">
         <is>
           <t>dispositif destiné à être introduit en totalité ou en partie dans le corps humain et à y demeurer après l'intervention</t>
         </is>
@@ -6381,7 +6413,7 @@
 </t>
         </is>
       </c>
-      <c r="I13" s="47" t="inlineStr">
+      <c r="I13" s="53" t="inlineStr">
         <is>
           <t>hulpmiddel dat bestemd is om geheel of gedeeltelijk in het menselijk lichaam te worden gebracht en daar na de ingreep te blijven</t>
         </is>
@@ -6391,7 +6423,7 @@
           <t>bijv. kalibratie, vervanging van de batterij, aanpassing van een prothese, aansluiting van een VAC-systeem voor wondverzorging, enz.), en dat een centraal onderdeel van de procedure vormt. De koppeling vindt plaats via een verwijzing naar een Device-bron.</t>
         </is>
       </c>
-      <c r="K13" s="48" t="inlineStr">
+      <c r="K13" s="51" t="inlineStr">
         <is>
           <t>device intended to be introduced wholly or partly into the human body and to remain there after the procedure</t>
         </is>
@@ -6414,7 +6446,7 @@
       <c r="F14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="46" t="inlineStr">
+      <c r="G14" s="52" t="inlineStr">
         <is>
           <t>identifiant attribué par le fabricant à l'ensemble des unités produites au cours d'un même cycle de fabrication</t>
         </is>
@@ -6424,12 +6456,12 @@
           <t>(Par exemple: Vaccin, appareil,...)</t>
         </is>
       </c>
-      <c r="I14" s="47" t="inlineStr">
+      <c r="I14" s="53" t="inlineStr">
         <is>
           <t>identificatie die de fabrikant toekent aan alle eenheden die in eenzelfde productiecyclus zijn vervaardigd</t>
         </is>
       </c>
-      <c r="K14" s="48" t="inlineStr">
+      <c r="K14" s="51" t="inlineStr">
         <is>
           <t>identifier assigned by the manufacturer to all units produced in the same manufacturing cycle</t>
         </is>
@@ -6454,24 +6486,34 @@
           <t>*</t>
         </is>
       </c>
-      <c r="G15" s="46" t="inlineStr">
+      <c r="G15" s="52" t="inlineStr">
         <is>
           <t>informations complémentaires relatives au contenu du CareSet, exprimées en texte libre</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>Une note n'est pas structurée. Il n'y a pas de VS associé. Une note ne contient pas de données sensibles. Ex: Niss du patient,Nom, etc…</t>
-        </is>
-      </c>
-      <c r="I15" s="48" t="inlineStr">
+      <c r="H15" s="47" t="inlineStr">
+        <is>
+          <t>Une note n'est pas structurée et n'a pas de ValueSet associé. Une note ne doit pas contenir de données identifiantes ou sensibles (par ex. NISS du patient, nom, adresse).</t>
+        </is>
+      </c>
+      <c r="I15" s="51" t="inlineStr">
         <is>
           <t>aanvullende informatie over de inhoud van de CareSet, uitgedrukt in vrije tekst</t>
         </is>
       </c>
-      <c r="K15" s="48" t="inlineStr">
+      <c r="J15" s="48" t="inlineStr">
+        <is>
+          <t>Een note is niet gestructureerd en heeft geen bijbehorende ValueSet. Een note mag geen identificerende of gevoelige gegevens bevatten (bijv. NISS van de patiënt, naam, adres).</t>
+        </is>
+      </c>
+      <c r="K15" s="51" t="inlineStr">
         <is>
           <t>Additional information related to the CareSet content in free text format</t>
+        </is>
+      </c>
+      <c r="L15" s="48" t="inlineStr">
+        <is>
+          <t>A note is unstructured and has no associated ValueSet. A note must not contain identifying or sensitive data (for example the patient's NISS, name or address).</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6528,7 @@
           <t>Originating Request</t>
         </is>
       </c>
-      <c r="G16" s="46" t="inlineStr">
+      <c r="G16" s="52" t="inlineStr">
         <is>
           <t>demande de soins ou de prestation dont l'exécution est enregistrée par le CareSet</t>
         </is>
@@ -6496,7 +6538,7 @@
           <t>Ex: un IRM basé sur une prescription d'imagerie, une dispensation d'un medicament basé sur une prescription médicamenteuse</t>
         </is>
       </c>
-      <c r="I16" s="47" t="inlineStr">
+      <c r="I16" s="53" t="inlineStr">
         <is>
           <t>aanvraag voor zorg of verstrekking waarvan de uitvoering door de CareSet wordt geregistreerd</t>
         </is>
@@ -6506,7 +6548,7 @@
           <t>Bijvoorbeeld: een MRI-scan op basis van een beeldvormingsvoorschrift, het verstrekken van een geneesmiddel op basis van een medicijnvoorschrift</t>
         </is>
       </c>
-      <c r="K16" s="48" t="inlineStr">
+      <c r="K16" s="51" t="inlineStr">
         <is>
           <t>request for care or service whose execution is recorded by the CareSet</t>
         </is>
@@ -6518,12 +6560,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C17" s="48" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>Part Of</t>
         </is>
       </c>
-      <c r="G17" s="46" t="inlineStr">
+      <c r="G17" s="52" t="inlineStr">
         <is>
           <t>CareSet englobant dont l'enregistrement courant constitue un composant</t>
         </is>
@@ -6533,7 +6575,7 @@
           <t>Par exemple:  Une Observation qui fait parti d'une autre Observation, Une biopsie qui fait parti d'une intervention chirugicale</t>
         </is>
       </c>
-      <c r="I17" s="47" t="inlineStr">
+      <c r="I17" s="53" t="inlineStr">
         <is>
           <t>omvattende CareSet waarvan de huidige registratie een onderdeel vormt</t>
         </is>
@@ -6543,12 +6585,12 @@
           <t>Bijvoorbeeld: een biopsie die deel uitmaakt van een chirurgische ingreep</t>
         </is>
       </c>
-      <c r="K17" s="48" t="inlineStr">
+      <c r="K17" s="51" t="inlineStr">
         <is>
           <t>encompassing CareSet of which the current record forms a component</t>
         </is>
       </c>
-      <c r="L17" s="48" t="inlineStr">
+      <c r="L17" s="51" t="inlineStr">
         <is>
           <t>For example: a biopsy that is part of a surgical intervention.</t>
         </is>
@@ -6571,7 +6613,7 @@
       <c r="F18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="46" t="inlineStr">
+      <c r="G18" s="52" t="inlineStr">
         <is>
           <t>La personne qui est l'objet des soins de santé auxquels le CareSet fait référence.</t>
         </is>
@@ -6581,7 +6623,7 @@
           <t>Le patient est représenté par l’identifiant unique qui doit être le N° de registre national du patient (NISS). mais dans certains cas, on peut autoriser un autre identifiant unique (comme le N° biss ou la combinaison du nom, prénom(s), date de naissance)</t>
         </is>
       </c>
-      <c r="I18" s="48" t="inlineStr">
+      <c r="I18" s="51" t="inlineStr">
         <is>
           <t>persoon op wie de zorg betrekking heeft waarnaar de registratie verwijst</t>
         </is>
@@ -6591,7 +6633,7 @@
           <t>De patiënt wordt aangeduid met een uniek identificatienummer, dat het nationale registratienummer van de patiënt (NISS) moet zijn. In bepaalde gevallen kan echter een ander uniek identificatienummer worden toegestaan (zoals het BISS-nummer of een combinatie van de achternaam, voornaam(en) en geboortedatum).</t>
         </is>
       </c>
-      <c r="K18" s="48" t="inlineStr">
+      <c r="K18" s="51" t="inlineStr">
         <is>
           <t>The person who is the subject of the healthcare to which the record (CareSet) refers</t>
         </is>
@@ -6614,7 +6656,7 @@
       <c r="F19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="46" t="inlineStr">
+      <c r="G19" s="52" t="inlineStr">
         <is>
           <t>personne qui a réalisé l'acte enregistré par le CareSet</t>
         </is>
@@ -6624,7 +6666,7 @@
           <t>L’identifiant unique doit être le N° de registre national du professionnel (NISS) ou le numéro BIS lorsque le NISS ou numéro BIS existe. Dans le cas contraire, on permet d’encoder éventuellement d’autres informations permettant de l’identifier. Ex : N° INAMI, nom et prénom, n° d’identifiant pour les prestataires étrangers…</t>
         </is>
       </c>
-      <c r="I19" s="48" t="inlineStr">
+      <c r="I19" s="51" t="inlineStr">
         <is>
           <t>persoon die de door de CareSet geregistreerde handeling heeft uitgevoerd</t>
         </is>
@@ -6634,12 +6676,12 @@
           <t>De unieke identificatiecode moet het nationale registratienummer van de beroepsbeoefenaar (NISS) zijn, of het BIS-nummer indien het NISS of het BIS-nummer bestaat. Indien dit niet het geval is, is het toegestaan om eventueel andere gegevens in te voeren waarmee de beroepsbeoefenaar kan worden geïdentificeerd. Bijvoorbeeld: RIZIV-nummer, voor- en achternaam, identificatienummer voor buitenlandse dienstverleners…</t>
         </is>
       </c>
-      <c r="K19" s="48" t="inlineStr">
+      <c r="K19" s="51" t="inlineStr">
         <is>
           <t>person who performed the act recorded by the CareSet</t>
         </is>
       </c>
-      <c r="L19" s="48" t="inlineStr">
+      <c r="L19" s="51" t="inlineStr">
         <is>
           <t>For example: administered the vaccine, performed the observation.</t>
         </is>
@@ -6651,7 +6693,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C20" s="48" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
         <is>
           <t>Recorded Date</t>
         </is>
@@ -6662,7 +6704,7 @@
       <c r="F20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="46" t="inlineStr">
+      <c r="G20" s="52" t="inlineStr">
         <is>
           <t>date à laquelle l'enregistrement a été saisi par le Recorder</t>
         </is>
@@ -6672,7 +6714,7 @@
           <t>(Date de la dernière mise à jour). Permet la gestion de l'historisation du CareSet via le couple Business Identifier - RecordedDate. Qui assure l'accès à la dernière version du contenu.</t>
         </is>
       </c>
-      <c r="I20" s="47" t="inlineStr">
+      <c r="I20" s="53" t="inlineStr">
         <is>
           <t>datum waarop de registratie door de Recorder is ingevoerd</t>
         </is>
@@ -6682,12 +6724,12 @@
           <t xml:space="preserve"> (datum van de laatste update). Maakt het mogelijk om de historiek van de CareSet te beheren via het paar Business Identifier - RecordedDate. Dit zorgt ervoor dat de laatste versie van de inhoud toegankelijk is.</t>
         </is>
       </c>
-      <c r="K20" s="48" t="inlineStr">
+      <c r="K20" s="51" t="inlineStr">
         <is>
           <t>date on which the record was entered by the Recorder</t>
         </is>
       </c>
-      <c r="L20" s="48" t="inlineStr">
+      <c r="L20" s="51" t="inlineStr">
         <is>
           <t>Date of last update. Enables CareSet history management through the Business Identifier / RecordedDate pair, which ensures access to the latest version of the content.</t>
         </is>
@@ -6704,9 +6746,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Route</t>
+      <c r="C21" s="48" t="inlineStr">
+        <is>
+          <t>Route of Administration</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -6717,7 +6759,7 @@
       </c>
       <c r="G21" s="46" t="inlineStr">
         <is>
-          <t>voie par laquelle un produit est mis en contact avec l'organisme</t>
+          <t>voie par laquelle le produit pharmaceutique est introduit dans le corps ou entre en contact avec celui-ci</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
@@ -6727,7 +6769,7 @@
       </c>
       <c r="I21" s="47" t="inlineStr">
         <is>
-          <t>weg waarlangs een product in contact wordt gebracht met het lichaam</t>
+          <t>weg waarlangs het farmaceutisch product in het lichaam wordt binnengebracht of ermee in contact komt</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -6737,10 +6779,10 @@
       </c>
       <c r="K21" s="48" t="inlineStr">
         <is>
-          <t>path by which a product is brought into contact with the body</t>
-        </is>
-      </c>
-      <c r="L21" s="48" t="inlineStr">
+          <t>path by which the pharmaceutical product is introduced into the body or comes into contact with it</t>
+        </is>
+      </c>
+      <c r="L21" s="51" t="inlineStr">
         <is>
           <t>See ValueSet VS_Route.</t>
         </is>
@@ -6752,7 +6794,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C22" s="48" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>Serial Number</t>
         </is>
@@ -6763,7 +6805,7 @@
       <c r="F22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="46" t="inlineStr">
+      <c r="G22" s="52" t="inlineStr">
         <is>
           <t>identifiant attribué par le fabricant à un exemplaire déterminé d'un dispositif</t>
         </is>
@@ -6773,7 +6815,7 @@
           <t>(pour un appareil uniquement)</t>
         </is>
       </c>
-      <c r="I22" s="47" t="inlineStr">
+      <c r="I22" s="53" t="inlineStr">
         <is>
           <t>identificatie die de fabrikant toekent aan één welbepaald exemplaar van een hulpmiddel</t>
         </is>
@@ -6783,7 +6825,7 @@
           <t>(alleen voor één apparaat)</t>
         </is>
       </c>
-      <c r="K22" s="48" t="inlineStr">
+      <c r="K22" s="51" t="inlineStr">
         <is>
           <t>identifier assigned by the manufacturer to one individual device</t>
         </is>
@@ -6795,7 +6837,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C23" s="48" t="inlineStr">
+      <c r="C23" s="51" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -6806,7 +6848,7 @@
       <c r="F23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="46" t="inlineStr">
+      <c r="G23" s="52" t="inlineStr">
         <is>
           <t>état de l'enregistrement dans son cycle de vie</t>
         </is>
@@ -6816,7 +6858,7 @@
           <t>Ex : Final, Correcte, Canceled, Entered_in_err</t>
         </is>
       </c>
-      <c r="I23" s="47" t="inlineStr">
+      <c r="I23" s="53" t="inlineStr">
         <is>
           <t>toestand van de registratie in haar levenscyclus</t>
         </is>
@@ -6826,12 +6868,12 @@
           <t>Ex : Final, Corrected, Canceled, Entered_in_err</t>
         </is>
       </c>
-      <c r="K23" s="48" t="inlineStr">
+      <c r="K23" s="51" t="inlineStr">
         <is>
           <t>state of the record within its lifecycle</t>
         </is>
       </c>
-      <c r="L23" s="48" t="inlineStr">
+      <c r="L23" s="51" t="inlineStr">
         <is>
           <t>For example: final, corrected, cancelled, entered-in-error.</t>
         </is>
@@ -6843,7 +6885,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C24" s="48" t="inlineStr">
+      <c r="C24" s="51" t="inlineStr">
         <is>
           <t>Used Device</t>
         </is>
@@ -6856,7 +6898,7 @@
           <t>*</t>
         </is>
       </c>
-      <c r="G24" s="46" t="inlineStr">
+      <c r="G24" s="52" t="inlineStr">
         <is>
           <t>dispositif médical mis en œuvre pour réaliser l'acte enregistré</t>
         </is>
@@ -6867,7 +6909,7 @@
 Les petits instruments standard tels que les scalpels et les seringues ne sont pas enregistrés.Le lien s’effectue via une référence vers une ressource Device.</t>
         </is>
       </c>
-      <c r="I24" s="47" t="inlineStr">
+      <c r="I24" s="53" t="inlineStr">
         <is>
           <t>medisch hulpmiddel dat wordt ingezet om de geregistreerde handeling uit te voeren</t>
         </is>
@@ -6877,7 +6919,7 @@
           <t>(chirurgische robot, bewakingsapparaat, …).</t>
         </is>
       </c>
-      <c r="K24" s="48" t="inlineStr">
+      <c r="K24" s="51" t="inlineStr">
         <is>
           <t>medical device used to carry out the recorded act</t>
         </is>
@@ -6889,56 +6931,44 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="C25" s="48" t="inlineStr">
+      <c r="C25" s="51" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Certainty</t>
-        </is>
-      </c>
+      <c r="D25" s="48" t="n"/>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="46" t="inlineStr">
+      <c r="G25" s="52" t="inlineStr">
         <is>
           <t>degré de confirmation attribué à l'information enregistrée</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>Observation.Code : Tension artérielle (75367002)
-Component.Code :
- 271649006 : Pression artérielle systolique
- 271650006 : Pression artérielle diastolique Code du composant du CareSet Observation. 
-Ce composant est uniquement utilisé pour les mesures de la tension artérielle dans le cadre du CareSet ClinicalObservation :</t>
-        </is>
-      </c>
-      <c r="I25" s="48" t="inlineStr">
+      <c r="H25" s="47" t="inlineStr">
+        <is>
+          <t>Ex : confirmed, unconfirmed, refuted, entered-in-error.</t>
+        </is>
+      </c>
+      <c r="I25" s="51" t="inlineStr">
         <is>
           <t>graad van bevestiging van de geregistreerde informatie</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>"Observatie.Code: Bloeddruk (75367002)
-Component.Code:
- 271649006: Systolische bloeddruk
- 271650006: Diastolische bloeddruk Code van de component van de CareSet Observatie.
-Deze component wordt uitsluitend gebruikt voor bloeddrukmetingen in het kader van de CareSet ClinicalObservation:"</t>
-        </is>
-      </c>
-      <c r="K25" s="48" t="inlineStr">
+      <c r="J25" s="47" t="inlineStr">
+        <is>
+          <t>Bijv.: confirmed, unconfirmed, refuted, entered-in-error.</t>
+        </is>
+      </c>
+      <c r="K25" s="51" t="inlineStr">
         <is>
           <t>degree of confirmation assigned to the recorded information</t>
         </is>
       </c>
-      <c r="L25" s="48" t="inlineStr">
+      <c r="L25" s="51" t="inlineStr">
         <is>
           <t>For example: confirmed, unconfirmed, refuted, entered-in-error.</t>
         </is>
